--- a/tasks/finalpool/fetch-wc-inventory-forecast-excel-gcal-email/groundtruth_workspace/Inventory_Forecast_Report.xlsx
+++ b/tasks/finalpool/fetch-wc-inventory-forecast-excel-gcal-email/groundtruth_workspace/Inventory_Forecast_Report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,20 +467,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(Renewed) JBL Flip 4 Portable Wireless Speaker with Powerful Bass &amp; Mic (Squad)</t>
+          <t>(Renewed) Havells FHVVEDXOWH08 200mm Exhaust Fan (White)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -491,20 +491,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CraftDev A500MB Portable Paper Trimmer 12 Inch Cut</t>
+          <t>(Renewed) JBL Flip 4 Portable Wireless Speaker with Powerful Bass &amp; Mic (Squad)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D3" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -515,20 +515,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LIMBANI BROTHERS™ Automatic Vacuum Sealing Machine | Vacuum Sealer for Flatbreads, Nuts, Vegetables, Fruits, Dry-Fruits | ...</t>
+          <t>30kg digital scale for shop and kitchen green display 72hrs battery backup weight machine</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>197</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>2.19</v>
+        <v>0.43</v>
       </c>
       <c r="E4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -539,20 +539,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MICROSMT M83 Smart LED TV (75-SMT-4K/1024/08-KSR-22),75 Inches.</t>
+          <t>AGARO Adjustable Camera Tripod Stand with Mobile Phones Clip &amp; Camera Holder, Supports Up to 3 Kgs, 66 inches (167 cm) Tall</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="D5" t="n">
-        <v>2.11</v>
+        <v>1.52</v>
       </c>
       <c r="E5" t="n">
-        <v>13.3</v>
+        <v>18.4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -563,44 +563,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIHARA Wood Smart Multipurpose Foldable Laptop Table with Cup Holder Ergonomic &amp; Rounded Edges (Black)</t>
+          <t>AmazonBasics Expanding File Folder, Letter Size (Fits A4 Paper) - Black - with 13 pockets</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>199</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
-        <v>2.21</v>
+        <v>0.68</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OnePlus 138.7 cm (55 inches) U Series 4K LED Smart Android TV 55U1S (Black)</t>
+          <t>Ambrane Mobile Holding Tabletop Stand, 180 Perfect View, Height Adjustment, Wide Compatibility, Multipurpose, Anti-Skid De...</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="D7" t="n">
-        <v>2.04</v>
+        <v>1.56</v>
       </c>
       <c r="E7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -611,20 +611,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oppo Enco Air 3 True Wireless in-Ear Earbuds with 25hrs Playtime, Fast Charging,13.4mm Driver &amp; BT v5.3 (Glaze White)</t>
+          <t>Anne Klein New York Womens Stainless Steel Analogue Watch - AK3344NVRG (Blue_Free Size)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>195</v>
+        <v>42</v>
       </c>
       <c r="D8" t="n">
-        <v>2.17</v>
+        <v>0.47</v>
       </c>
       <c r="E8" t="n">
-        <v>7.4</v>
+        <v>19.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -635,22 +635,1798 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Artis 65Watt Universal Laptop Adapter with 8 Interchangeable Connector pins (Power Cord Included) Compatible with Dell/HP/...</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Belkin Ultra HD High Speed HDMI® Cable, Supports 8K and 4K, HDMI 2.1 Certified, Dolby Vision, Black</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>80</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>boAt Dual Port Rapid 5V Car Charger (Qualcomm Certified) Smart Charging with Quick Charge 3.0 for Cellular Phones (Black)...</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>boAt Wave Call Smart Watch, Smart Talk with Advanced Dedicated Bluetooth Calling Chip, 1.69” HD Display with 550 NITS &amp; 7...</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C12" t="n">
+        <v>170</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>boAt Wave Lite Smartwatch with 1.69 Inches(4.29cm) HD Display, Heart Rate &amp; SpO2 Level Monitor, Multiple Watch Faces, Acti...</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C13" t="n">
+        <v>137</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Boult Audio Powerbuds True Wireless in Ear Earbuds with 120H Playtime, in-Built Powerbank, Type-C Fast Charging, Made in I...</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>35</v>
+      </c>
+      <c r="C14" t="n">
+        <v>27</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BOXTUDIO®- LIGHTBOX- Tabletop Portable PhotoStudio(40x40x40cms)- Product Photography Light Tent- Think Inside The Box !-10...</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>183</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Canon M50 Mark II 15-45mm f3.5-6.3 is STM</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="n">
+        <v>108</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CASEOLOGY by Spigen Athlex Back Cover Case Compatible with Samsung Galaxy S23 Ultra (TPU and PC | Active Black)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>152</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Citizen Eco-Drive Analog Mother of Pearl Dial Women's Watch-EW2543-85D</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>24</v>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CraftDev A500MB Portable Paper Trimmer 12 Inch Cut</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>192</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Craftwings Handheld Press Fan Mini Kids Fan Toy Plaything Hand Press Fan Cartoon Fan Toy (1)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>41</v>
+      </c>
+      <c r="C20" t="n">
+        <v>84</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E20" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DALI ALTECO C-1 100 Watt 2.0 Channel Speaker with Dolby Atmos (Black)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>25</v>
+      </c>
+      <c r="C21" t="n">
+        <v>167</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dell S2721HNM-Grey 27" FHD 1920 x 1080 @75 Hz |Minimalistic Design | IPS Panel |Brightness: 300 cd/m²|Colour Gamut: 99% sR...</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dlx hmt Women Watch Casual Dress Analog Luxury Quartz Wrist Watches Stainless Steel Watch (Silver, Set of 2)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>76</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Eloies® Tripod for Mobile and Camera Jaguar Series Alluminum Made 3 Way Pan Head Photo Video Tripod Heavy Duty Tripod Stan...</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>168</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FOLX FMS1210 Metal Stainless Steel Bands Compatible with Apple Watch Bands, Loop Magnetic Milanese Mesh Strap for iWatch S...</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>90</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fujifilm Instax Stained Glass Instant Film, 10 Sheets</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" t="n">
+        <v>77</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E26" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>In-Ear Headphone For Samsung Galaxy A20, A 20 In- Ear Headphone | Earphones | Headphone| Handsfree | Headset | Universal H...</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>84</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Infinity (JBL Glide 500, 20 Hrs Playtime with Quick Charge, Wireless On Ear Headphone with Mic, Deep Bass, Dual Equalizer,...</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>124</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>INVANTER 2022 Model Smart TV FRAMLESS Android 43 INCH-SR 2 E</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>62</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IVELECT USB Male To 3RCA Female Video AV A/V Converter Cable Adapter For HDTV TV</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>19</v>
+      </c>
+      <c r="C30" t="n">
+        <v>173</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>JUDEE Keyboard Cleaning Brush 7 in 1 Kit, Portable Keyboard Tools Including Screen Dust Brush, Airpod Cleaner Per with Key...</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C31" t="n">
+        <v>165</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kingland Analogue Heart Dial Magnetic Metal Strap Girl's and Women's Watch(Watch-06)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>60</v>
+      </c>
+      <c r="C32" t="n">
+        <v>13</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E32" t="n">
+        <v>428.6</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LED TV ASIN 55-SR 6 R</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>36</v>
+      </c>
+      <c r="C33" t="n">
+        <v>148</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E33" t="n">
+        <v>22</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Lenovo Tab P11 5G FHD (11 inch (27.94 cm), 6 GB, 128 GB, Wi-Fi+LTE, Calling), Storm Grey with Qualcomm Snapdragon Processo...</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>140</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Levelplus Jack Neckband Bluetooth Headset (Grey in The Ear)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>55</v>
+      </c>
+      <c r="C35" t="n">
+        <v>40</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E35" t="n">
+        <v>125</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LG 139 cm (55 Inches) Nanocell Series 4K Ultra HD Smart LED TV 55NANO80SQA (Black) (2022 Model)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>54</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LIMBANI BROTHERS™ Automatic Vacuum Sealing Machine | Vacuum Sealer for Flatbreads, Nuts, Vegetables, Fruits, Dry-Fruits | ...</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>21</v>
+      </c>
+      <c r="C37" t="n">
+        <v>197</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MAONO AU-100 Auxiliary Omnidirectional Lavalier Clip On Collar Microphone for Mobile Phone, Camera with 6M Audio Cable, 3....</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" t="n">
+        <v>56</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mi Extended Warranty (1year) - Brand Authorised Plan for Mi TV Between 13999-19999(Email Delivery, No Physical Kit)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>108</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MICROSMT M83 Smart LED TV (75-SMT-4K/1024/08-KSR-22),75 Inches.</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>28</v>
+      </c>
+      <c r="C40" t="n">
+        <v>190</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E40" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MICROSMT Smart LED TV (32-SMT-FL/512/04-KSR-22),32 Inches</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>136</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MYJAS - Inverter battery cap level indicator white with warranty (30mm - set of 6)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>25</v>
+      </c>
+      <c r="C42" t="n">
+        <v>147</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NIHARA Wood Smart Multipurpose Foldable Laptop Table with Cup Holder Ergonomic &amp; Rounded Edges (Black)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>11</v>
+      </c>
+      <c r="C43" t="n">
+        <v>199</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Nikrim™ Portable Blender, Personal Mini Bottle Travel Electric Smoothie Blender Maker Fruit Juicer Cup, with 13oz Bottles,...</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>15</v>
+      </c>
+      <c r="C44" t="n">
+        <v>13</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E44" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NP-BN1 Rechargeable Lithium-Ion Camera Battery Compatible with Sony Camera DSC-W710 DSC-W730 DSC-W810 DSC-W830 DSC-W530 DS...</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>12</v>
+      </c>
+      <c r="C45" t="n">
+        <v>56</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E45" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OnePlus 138.7 cm (55 inches) U Series 4K LED Smart Android TV 55U1S (Black)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>20</v>
+      </c>
+      <c r="C46" t="n">
+        <v>184</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>OnePlus Buds Pro Bluetooth Truly Wireless in Ear Earbuds with mic, Smart Adaptive Noise Cancellation, 10 Minutes Warp Char...</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>7</v>
+      </c>
+      <c r="C47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E47" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>OpenTech® Tempered Glass Screen Protector Compatible for Nothing Phone 1 with Edge to Edge Coverage and Easy Installation kit</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>12</v>
+      </c>
+      <c r="C48" t="n">
+        <v>33</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E48" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Oppo Enco Air 3 True Wireless in-Ear Earbuds with 25hrs Playtime, Fast Charging,13.4mm Driver &amp; BT v5.3 (Glaze White)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>195</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Oraimo 25.5W 4 Ports USB Charger, 5.1A USB Wall Charger Phone Adapter Compatible for iPhone 13/13 Mini/13 Pro Max/12/12 Pr...</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B50" t="n">
         <v>20</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C50" t="n">
         <v>195</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D50" t="n">
         <v>2.17</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E50" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ORICO SD Card Holder, Water-Resistant SD Card Storage, Professional Anti-Shock Memory Card Carrying Case for 26 Micro SD S...</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>32</v>
+      </c>
+      <c r="C51" t="n">
+        <v>104</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E51" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PAMPA Wireless Portable Bluetooth Speaker with Handle Compatible with All Devices for Home/Office/Party/Beach.</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>11</v>
+      </c>
+      <c r="C52" t="n">
+        <v>32</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E52" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Pentonic Multicolor Gel Pen With Hard Box Case | 0.6 mm-1.0 mm | Sleek Matt Finish, Featherlite feel | Waterproof Gel Ink,...</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>11</v>
+      </c>
+      <c r="C53" t="n">
+        <v>17</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E53" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PFN Analog DW Maroon Colour White dial Mens Watch Womens Watch</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>116</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PJ Masks Catboy Kids Headphones by CozyPhones - Over The Ear Headband Headphones - Volume Limited with Thin Speakers &amp; Sof...</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>36</v>
+      </c>
+      <c r="C55" t="n">
+        <v>19</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E55" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>POPIO Tempered Glass Compatible for iPhone 6; iPhone 6S; iPhone 7; iPhone 8 (Transparent) Full Screen Coverage (Except Edg...</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" t="n">
+        <v>54</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Power Guard 80 cm (32 inches) Frameless HD Ready Smart LED TV PG32FSVC (Black)</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>18</v>
+      </c>
+      <c r="C57" t="n">
+        <v>144</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Rambutan Opto Coupler 1.8</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" t="n">
+        <v>123</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E58" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Robustrion Smart Trifold Hard Back Flip Stand Case Cover for Lenovo Tab M10 HD 2nd Gen TB-X306X / Smart Tab M10 HD 2nd Gen...</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="n">
+        <v>135</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Samsung 1m 09cm (43") Smart Monitor with Built-in Speaker - LS43AM704UWXXL</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="n">
+        <v>117</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SeCro 3.5mm Female to 6.35mm Male Plug Stereo Audio Auxiliary Jack Converter for Charging Adapter (Golden)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>26</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Shopnet Wireless Bluetooth Speaker TG113 For Huawei MediaPad T2 7.0 Pro Ultra Boost Bass with DJ Sound Portable Home Speak...</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>26</v>
+      </c>
+      <c r="C62" t="n">
+        <v>123</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E62" t="n">
+        <v>19</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Shopnet Wireless Bluetooth Speaker TG113 For Samsung Galaxy Tab A 7.0 9 (2016), Samsung Galaxy Tab A 8.0, Samsung Galaxy T...</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" t="n">
+        <v>160</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Silencer Panels, Flame Retardant Sound‑Absorption, Polyester Fiber Stable for Recording Studio Home Theater Black</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>156</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SONATA GOLD Series CCTV Mini WiFi Magnet Camera, Wireless CCTV 1080P IR Night Viewing 2 Way Audio Smart Surveillance Camer...</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>12</v>
+      </c>
+      <c r="C65" t="n">
+        <v>172</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sony Extra Bass MDR-XB450AP On-Ear Wired Headphones with Mic (Black)</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>10</v>
+      </c>
+      <c r="C66" t="n">
+        <v>72</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Techzere Portable Rechargeable Handsfree Neck Fan with LED Red &amp; Black</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>39</v>
+      </c>
+      <c r="C67" t="n">
+        <v>46</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E67" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TELESIN Battery for GoPro Hero 11/10/9 Camera with 1750mAh Rechargeable Battery | Camera Battery (1 X Charger &amp; 2 X Battery)</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E68" t="n">
+        <v>50</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TheGiftKart Flip Back Cover Case for OnePlus Nord CE 2 LITE 5G | Dual-Color Leather Finish | Inbuilt Stand &amp; Pockets | Wal...</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>80</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TheGiftKart Shockproof Crystal Clear Back Cover Case for Redmi A1 | 360 Degree Protection | Protective Design | Transparen...</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="n">
+        <v>102</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Tiitan N2 Wireless Bluetooth In Ear Neckband Earphone with Mic (Black)</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E71" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tronica Super King 40W 5.1 Bluetooth Home Theater System with FM/PenDrive/Sd Card/Mobile/Aux Support &amp; Remote (5.1 Speaker...</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E72" t="n">
+        <v>200</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Type C Earphone AK-G Wired Earphone For Samsung Galaxy Note20 5G , Samsung Galaxy Note 20 5G USB C Headphones Type C Earph...</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>30</v>
+      </c>
+      <c r="C73" t="n">
+        <v>32</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E73" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TYPE-C Earphone for OnePlus 8 Pro , OnePlus Eight Pro in Ear Type C Wired Earphones with Mic, Braided 1.2 Metre Cable, Met...</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="n">
+        <v>139</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VIBLITZ® 3 in 1 Universal Stabilizer C-Shape Bracket Video Handheld Grip + Ball Head hot Shoe Adapter + Mobile Phone Clip ...</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>13</v>
+      </c>
+      <c r="C75" t="n">
+        <v>57</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E75" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Vivo Y56 5G (Black Engine, 8GB RAM, 128GB Storage) with No Cost EMI/Additional Exchange Offers</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>20</v>
+      </c>
+      <c r="C76" t="n">
+        <v>149</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E76" t="n">
+        <v>12</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Wireless Bluetooth Headphones Earphone For Huawei Honor 7A Neckband Earphone Bluetooth 5.0 Wireless Headphones with Hi-Fi ...</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>7</v>
+      </c>
+      <c r="C77" t="n">
+        <v>138</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WorldCare® Durable VGA Wall Socket Module Modular Wallplate with Frame Directly Plug</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>17</v>
+      </c>
+      <c r="C78" t="n">
+        <v>76</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E78" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>XTOUCH XTBC01 XBass Rich Bass and Noise Cancellation Earphone with Type C Port, 13mm Driver, Inline Mic &amp; Volume Controlle...</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="n">
+        <v>155</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Zaha New Generation Digital Red LED Watch for Boys, Girls &amp; Kids Pack of 2. (White &amp; Black)</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>25</v>
+      </c>
+      <c r="C80" t="n">
+        <v>144</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E80" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Zavia French Fox ENC Earbuds, Dolby Atmos,50 Hrs Playtime,500 mAh Battery,Made in India,Fast Charge, 2 Mics for Perfect Ca...</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>44</v>
+      </c>
+      <c r="C81" t="n">
+        <v>66</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E81" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ZEBRONICS Zeb-100HB 4 Ports USB Hub for Laptop, PC Computers, Plug &amp; Play, Backward Compatible - Black</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>6</v>
+      </c>
+      <c r="C82" t="n">
+        <v>166</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ZETONES Electric Mini Cooking Pot, Electric Cooker Steamer (Blue, 1.5 L, 600-Watts, Outer Lid)</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>21</v>
+      </c>
+      <c r="C83" t="n">
+        <v>153</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E83" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -789,7 +2565,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
@@ -799,7 +2575,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -809,7 +2585,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -819,7 +2595,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.7</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
